--- a/eval_output/資材課_王秀雯_評分表.xlsx
+++ b/eval_output/資材課_王秀雯_評分表.xlsx
@@ -749,7 +749,11 @@
           <t>朱冠瑋</t>
         </is>
       </c>
-      <c r="F6" s="6" t="n"/>
+      <c r="F6" s="6" t="inlineStr">
+        <is>
+          <t>楊玉鳳</t>
+        </is>
+      </c>
       <c r="G6" s="6" t="n"/>
       <c r="H6" s="6" t="n"/>
       <c r="I6" s="6" t="n"/>

--- a/eval_output/資材課_王秀雯_評分表.xlsx
+++ b/eval_output/資材課_王秀雯_評分表.xlsx
@@ -182,7 +182,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -212,6 +212,9 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -226,6 +229,10 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+      <protection locked="0" hidden="0"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -286,8 +293,9 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
+      <protection locked="0" hidden="0"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -727,7 +735,7 @@
         </is>
       </c>
       <c r="C5" s="3">
-        <f>COUNTIF(D6:P6,"&lt;&gt;")</f>
+        <f>COUNTIF(D6:F6,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -795,24 +803,30 @@
           <t>0~10分</t>
         </is>
       </c>
+      <c r="D8" s="11" t="n"/>
+      <c r="E8" s="11" t="n"/>
+      <c r="F8" s="11" t="n"/>
       <c r="G8" s="3" t="n"/>
       <c r="H8" s="9" t="n"/>
       <c r="I8" s="9" t="n"/>
       <c r="J8" s="6" t="n"/>
     </row>
     <row r="9" ht="31" customHeight="1">
-      <c r="B9" s="11" t="inlineStr">
+      <c r="B9" s="12" t="inlineStr">
         <is>
           <t>公司辦法考核</t>
         </is>
       </c>
-      <c r="C9" s="11" t="inlineStr">
+      <c r="C9" s="12" t="inlineStr">
         <is>
           <t>根據考核固定成績</t>
         </is>
       </c>
-      <c r="H9" s="11" t="n"/>
-      <c r="I9" s="11" t="n"/>
+      <c r="D9" s="11" t="n"/>
+      <c r="E9" s="11" t="n"/>
+      <c r="F9" s="11" t="n"/>
+      <c r="H9" s="12" t="n"/>
+      <c r="I9" s="12" t="n"/>
       <c r="J9" s="6" t="n"/>
     </row>
     <row r="10" ht="53" customHeight="1">
@@ -821,12 +835,12 @@
           <t>團隊溝通協調能力20%</t>
         </is>
       </c>
-      <c r="B10" s="12" t="inlineStr">
+      <c r="B10" s="13" t="inlineStr">
         <is>
           <t>受評者的溝通協調與配合度</t>
         </is>
       </c>
-      <c r="C10" s="13" t="inlineStr">
+      <c r="C10" s="14" t="inlineStr">
         <is>
           <t>✓非常願意溝通協調且配合度極高 (16-20)
 ✓願意溝通協調且配合度高 (12-15)
@@ -835,19 +849,22 @@
 ✓非常不願意溝通協調且配合度極低 (0-3)</t>
         </is>
       </c>
+      <c r="D10" s="11" t="n"/>
+      <c r="E10" s="11" t="n"/>
+      <c r="F10" s="11" t="n"/>
       <c r="G10" s="3" t="n"/>
-      <c r="H10" s="11" t="n"/>
+      <c r="H10" s="12" t="n"/>
       <c r="I10" s="9" t="n"/>
       <c r="J10" s="6" t="n"/>
     </row>
     <row r="11" ht="53" customHeight="1">
       <c r="A11" s="8" t="n"/>
-      <c r="B11" s="14" t="inlineStr">
+      <c r="B11" s="15" t="inlineStr">
         <is>
           <t>※印象中你對受評者在主管交辦的任務完成率</t>
         </is>
       </c>
-      <c r="C11" s="15" t="inlineStr">
+      <c r="C11" s="16" t="inlineStr">
         <is>
           <t>✓對於主管交辦的任務均能完成 (15)
 ✓對於主管交辦的任務均能完成90%以上 (13-14)
@@ -858,37 +875,42 @@
 ✓對於主管交辦的任務常說”我不會、我不要、不是我”(0~1)</t>
         </is>
       </c>
-      <c r="D11" s="6" t="n"/>
-      <c r="G11" s="16" t="n"/>
+      <c r="D11" s="17" t="n"/>
+      <c r="E11" s="11" t="n"/>
+      <c r="F11" s="11" t="n"/>
+      <c r="G11" s="18" t="n"/>
       <c r="H11" s="9" t="n"/>
-      <c r="I11" s="17" t="n"/>
+      <c r="I11" s="19" t="n"/>
       <c r="J11" s="6" t="n"/>
     </row>
     <row r="12" ht="57" customHeight="1">
-      <c r="A12" s="18" t="inlineStr">
+      <c r="A12" s="20" t="inlineStr">
         <is>
           <t>工作態度
 15%</t>
         </is>
       </c>
-      <c r="B12" s="19" t="inlineStr">
+      <c r="B12" s="21" t="inlineStr">
         <is>
           <t>*低於等於3分或高於等於13分，請說明原因： ______________________</t>
         </is>
       </c>
+      <c r="D12" s="11" t="n"/>
+      <c r="E12" s="11" t="n"/>
+      <c r="F12" s="11" t="n"/>
       <c r="G12" s="3" t="n"/>
       <c r="H12" s="9" t="n"/>
       <c r="I12" s="9" t="n"/>
       <c r="J12" s="6" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="18" t="n"/>
-      <c r="B13" s="13" t="inlineStr">
+      <c r="A13" s="20" t="n"/>
+      <c r="B13" s="14" t="inlineStr">
         <is>
           <t>是否落實公司 ISO9001 及內部稽核／內控制度之執行</t>
         </is>
       </c>
-      <c r="C13" s="13" t="inlineStr">
+      <c r="C13" s="14" t="inlineStr">
         <is>
           <t>✓完整落實ISO9001與內稽內控機制，文件、流程、紀錄皆符合規範，並主動優化制度或提出改善措施(10)
 ✓大致落實制度要求，稽核資料齊全，偶有小缺失但能即時改善(8-9)
@@ -898,35 +920,40 @@
 ✓無執行相關制度或嚴重違反規範(0)</t>
         </is>
       </c>
-      <c r="D13" s="6" t="n"/>
+      <c r="D13" s="17" t="n"/>
+      <c r="E13" s="11" t="n"/>
+      <c r="F13" s="11" t="n"/>
       <c r="H13" s="9" t="n"/>
-      <c r="I13" s="17" t="n"/>
+      <c r="I13" s="19" t="n"/>
       <c r="J13" s="6" t="n"/>
     </row>
     <row r="14" ht="47" customHeight="1">
-      <c r="A14" s="20" t="inlineStr">
+      <c r="A14" s="22" t="inlineStr">
         <is>
           <t>領導統御25%</t>
         </is>
       </c>
-      <c r="B14" s="21" t="inlineStr">
+      <c r="B14" s="23" t="inlineStr">
         <is>
           <t>*低於等於3分或最高分，請敘述狀況：_________________________</t>
         </is>
       </c>
-      <c r="G14" s="16" t="n"/>
+      <c r="D14" s="11" t="n"/>
+      <c r="E14" s="11" t="n"/>
+      <c r="F14" s="11" t="n"/>
+      <c r="G14" s="18" t="n"/>
       <c r="H14" s="9" t="n"/>
-      <c r="I14" s="17" t="n"/>
+      <c r="I14" s="19" t="n"/>
       <c r="J14" s="6" t="n"/>
     </row>
     <row r="15" ht="47" customHeight="1">
-      <c r="A15" s="20" t="n"/>
-      <c r="B15" s="14" t="inlineStr">
+      <c r="A15" s="22" t="n"/>
+      <c r="B15" s="15" t="inlineStr">
         <is>
           <t>※印象中你對受評者在指導與覆核部屬方面，願意給幾分</t>
         </is>
       </c>
-      <c r="C15" s="15" t="inlineStr">
+      <c r="C15" s="16" t="inlineStr">
         <is>
           <t>✓經常主動指導(領導)部屬 (13-15)
 ✓需經部屬提出並樂意指導(領導) (9-12)
@@ -934,18 +961,23 @@
 ✓部屬提出仍不指導(領導) (0~4)</t>
         </is>
       </c>
-      <c r="D15" s="6" t="n"/>
+      <c r="D15" s="17" t="n"/>
+      <c r="E15" s="11" t="n"/>
+      <c r="F15" s="11" t="n"/>
       <c r="H15" s="9" t="n"/>
       <c r="I15" s="9" t="n"/>
       <c r="J15" s="6" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="20" t="n"/>
-      <c r="B16" s="19" t="inlineStr">
+      <c r="A16" s="22" t="n"/>
+      <c r="B16" s="21" t="inlineStr">
         <is>
           <t>*低於等於6分或高於等於12分，請說明原因：________________</t>
         </is>
       </c>
+      <c r="D16" s="11" t="n"/>
+      <c r="E16" s="11" t="n"/>
+      <c r="F16" s="11" t="n"/>
       <c r="G16" s="6" t="n"/>
       <c r="H16" s="6" t="n"/>
       <c r="I16" s="6" t="n"/>
@@ -953,13 +985,13 @@
     </row>
     <row r="17" ht="61.5" customHeight="1">
       <c r="A17" s="8" t="n"/>
-      <c r="B17" s="13" t="inlineStr">
+      <c r="B17" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">你對於受評者在會議追蹤事項之執行、回覆與結案管理上，是否能依規定期限完成並有效追蹤事項進度之表現評價為何？
 </t>
         </is>
       </c>
-      <c r="C17" s="22" t="inlineStr">
+      <c r="C17" s="24" t="inlineStr">
         <is>
           <t>10分：會議追蹤事項皆能準時完成並主動追蹤，結案完整無需提醒
 7~9分：大多能準時完成，偶有延遲但能主動回覆並完成結案
@@ -967,36 +999,41 @@
 4分以下：經常延遲、未追蹤或未完成結案，影響會議執行成效或跨部門作業效率</t>
         </is>
       </c>
-      <c r="D17" s="6" t="n"/>
+      <c r="D17" s="17" t="n"/>
+      <c r="E17" s="11" t="n"/>
+      <c r="F17" s="11" t="n"/>
       <c r="G17" s="6" t="n"/>
       <c r="H17" s="6" t="n"/>
       <c r="I17" s="6" t="n"/>
       <c r="J17" s="6" t="n"/>
     </row>
     <row r="18" ht="42.5" customHeight="1">
-      <c r="A18" s="18" t="inlineStr">
+      <c r="A18" s="20" t="inlineStr">
         <is>
           <t>工作態度20%</t>
         </is>
       </c>
-      <c r="B18" s="21" t="inlineStr">
+      <c r="B18" s="23" t="inlineStr">
         <is>
           <t>*低於等於4分或高於等於9分，請說明原因：____________________</t>
         </is>
       </c>
+      <c r="D18" s="11" t="n"/>
+      <c r="E18" s="11" t="n"/>
+      <c r="F18" s="11" t="n"/>
       <c r="G18" s="6" t="n"/>
       <c r="H18" s="6" t="n"/>
       <c r="I18" s="6" t="n"/>
       <c r="J18" s="6" t="n"/>
     </row>
     <row r="19" ht="70.5" customHeight="1">
-      <c r="B19" s="23" t="inlineStr">
+      <c r="B19" s="25" t="inlineStr">
         <is>
           <t>※受評者對於文件審核、流程確認及內容正確性之管理能力評價
 共評者可依據平日文件簽核、退件紀錄、流程確認、跨部門溝通及會議執行情況進行評分。</t>
         </is>
       </c>
-      <c r="C19" s="24" t="inlineStr">
+      <c r="C19" s="26" t="inlineStr">
         <is>
           <t>✓受評者能有效審核文件內容，幾乎無退件或重大錯誤，並能主動發現問題與改善流程(10)
 ✓受評者大多能正確完成文件審核，僅偶有小幅修正或退件情況(5-9)
@@ -1004,22 +1041,36 @@
 ✓受評者未確實執行文件審核與流程確認，經常造成重工、退件或作業異常(0)</t>
         </is>
       </c>
-      <c r="D19" s="6" t="n"/>
+      <c r="D19" s="17" t="n"/>
+      <c r="E19" s="11" t="n"/>
+      <c r="F19" s="11" t="n"/>
       <c r="G19" s="6" t="n"/>
       <c r="H19" s="6" t="n"/>
       <c r="I19" s="6" t="n"/>
       <c r="J19" s="6" t="n"/>
     </row>
-    <row r="20" ht="52" customHeight="1"/>
+    <row r="20" ht="52" customHeight="1">
+      <c r="D20" s="11" t="n"/>
+      <c r="E20" s="11" t="n"/>
+      <c r="F20" s="11" t="n"/>
+    </row>
     <row r="21" ht="50.5" customHeight="1">
-      <c r="B21" s="25" t="n"/>
-      <c r="C21" s="26" t="inlineStr">
+      <c r="B21" s="27" t="n"/>
+      <c r="C21" s="28" t="inlineStr">
         <is>
           <t>總分</t>
         </is>
       </c>
-      <c r="D21" s="27">
+      <c r="D21" s="29">
         <f>SUM(D8:D20)</f>
+        <v/>
+      </c>
+      <c r="E21" s="29">
+        <f>SUM(E8:E20)</f>
+        <v/>
+      </c>
+      <c r="F21" s="29">
+        <f>SUM(F8:F20)</f>
         <v/>
       </c>
     </row>
@@ -1034,8 +1085,29 @@
 ), "⚠ 超標！", "")</f>
         <v/>
       </c>
+      <c r="E22" s="6">
+        <f>IF(OR(
+  AND(E21&gt;=90, COUNTIF($D$21:$Z$21, "&gt;=90")/COUNTA($D$21:$Z$21)&gt;0.05),
+  AND(E21&gt;=80,E21&lt;=89, (COUNTIF($D$21:$Z$21, "&gt;=80")-COUNTIF($D$21:$Z$21, "&gt;=90"))/COUNTA($D$21:$Z$21)&gt;0.2),
+  AND(E21&gt;=70,E21&lt;=79, (COUNTIF($D$21:$Z$21, "&gt;=70")-COUNTIF($D$21:$Z$21, "&gt;=80"))/COUNTA($D$21:$Z$21)&gt;0.4),
+  AND(E21&gt;=60,E21&lt;=69, (COUNTIF($D$21:$Z$21, "&gt;=60")-COUNTIF($D$21:$Z$21, "&gt;=70"))/COUNTA($D$21:$Z$21)&gt;0.3),
+  AND(E21&lt;=59, COUNTIF($D$21:$Z$21, "&lt;=59")/COUNTA($D$21:$Z$21)&gt;0.05)
+), "⚠ 超標！", "")</f>
+        <v/>
+      </c>
+      <c r="F22" s="6">
+        <f>IF(OR(
+  AND(F21&gt;=90, COUNTIF($D$21:$Z$21, "&gt;=90")/COUNTA($D$21:$Z$21)&gt;0.05),
+  AND(F21&gt;=80,F21&lt;=89, (COUNTIF($D$21:$Z$21, "&gt;=80")-COUNTIF($D$21:$Z$21, "&gt;=90"))/COUNTA($D$21:$Z$21)&gt;0.2),
+  AND(F21&gt;=70,F21&lt;=79, (COUNTIF($D$21:$Z$21, "&gt;=70")-COUNTIF($D$21:$Z$21, "&gt;=80"))/COUNTA($D$21:$Z$21)&gt;0.4),
+  AND(F21&gt;=60,F21&lt;=69, (COUNTIF($D$21:$Z$21, "&gt;=60")-COUNTIF($D$21:$Z$21, "&gt;=70"))/COUNTA($D$21:$Z$21)&gt;0.3),
+  AND(F21&lt;=59, COUNTIF($D$21:$Z$21, "&lt;=59")/COUNTA($D$21:$Z$21)&gt;0.05)
+), "⚠ 超標！", "")</f>
+        <v/>
+      </c>
     </row>
   </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1"/>
   <mergeCells count="19">
     <mergeCell ref="G8:G9"/>
     <mergeCell ref="D17:D18"/>
@@ -1121,7 +1193,7 @@
         </is>
       </c>
       <c r="C5" s="3">
-        <f>COUNTIF(D6:P6,"&lt;&gt;")</f>
+        <f>COUNTIF(D6:E6,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -1185,14 +1257,16 @@
 ✓不熟悉製程；錯誤率高；無法獨立作業或教導他人。(0-2) </t>
         </is>
       </c>
+      <c r="D8" s="11" t="n"/>
+      <c r="E8" s="11" t="n"/>
     </row>
     <row r="9" ht="63" customHeight="1">
-      <c r="B9" s="14" t="inlineStr">
+      <c r="B9" s="15" t="inlineStr">
         <is>
           <t>產品知識與設備保養管理（10 分）</t>
         </is>
       </c>
-      <c r="C9" s="14" t="inlineStr">
+      <c r="C9" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">✓熟知產品規格、品質要求、主要不良模式；保養確實、設備狀況佳。 (9-10) 
 ✓了解基本產品要求；保養紀錄完整；偶需提醒。 (7-8) 
@@ -1201,6 +1275,8 @@
 ✓不不懂產品、不做保養；設備狀況差，影響產線運作。(0-2) </t>
         </is>
       </c>
+      <c r="D9" s="11" t="n"/>
+      <c r="E9" s="11" t="n"/>
     </row>
     <row r="10" ht="65.5" customHeight="1">
       <c r="A10" s="8" t="inlineStr">
@@ -1208,12 +1284,12 @@
           <t>團隊溝通協調能力20%</t>
         </is>
       </c>
-      <c r="B10" s="12" t="inlineStr">
+      <c r="B10" s="13" t="inlineStr">
         <is>
           <t>受評者的溝通協調與配合度</t>
         </is>
       </c>
-      <c r="C10" s="13" t="inlineStr">
+      <c r="C10" s="14" t="inlineStr">
         <is>
           <t>✓非常願意溝通協調且配合度極高 (16-20)
 ✓願意溝通協調且配合度高 (12-15)
@@ -1222,15 +1298,17 @@
 ✓非常不願意溝通協調且配合度極低 (0-3)</t>
         </is>
       </c>
+      <c r="D10" s="11" t="n"/>
+      <c r="E10" s="11" t="n"/>
     </row>
     <row r="11" ht="65.5" customHeight="1">
       <c r="A11" s="8" t="n"/>
-      <c r="B11" s="14" t="inlineStr">
+      <c r="B11" s="15" t="inlineStr">
         <is>
           <t>對於主管交辦的任務</t>
         </is>
       </c>
-      <c r="C11" s="15" t="inlineStr">
+      <c r="C11" s="16" t="inlineStr">
         <is>
           <t>✓對於主管交辦的任務均能完成 (15)
 ✓對於主管交辦的任務均能完成90%以上 (13-14)
@@ -1241,28 +1319,31 @@
 ✓對於主管交辦的任務常說”我不會、我不要、不是我”(0~1)</t>
         </is>
       </c>
-      <c r="D11" s="6" t="n"/>
+      <c r="D11" s="17" t="n"/>
+      <c r="E11" s="11" t="n"/>
     </row>
     <row r="12" ht="49.5" customHeight="1">
-      <c r="A12" s="18" t="inlineStr">
+      <c r="A12" s="20" t="inlineStr">
         <is>
           <t>工作態度
 30%</t>
         </is>
       </c>
-      <c r="B12" s="19" t="inlineStr">
+      <c r="B12" s="21" t="inlineStr">
         <is>
           <t>*低於等於3分或高於等於13分，請說明原因： __________________________</t>
         </is>
       </c>
+      <c r="D12" s="11" t="n"/>
+      <c r="E12" s="11" t="n"/>
     </row>
     <row r="13" ht="49.5" customHeight="1">
-      <c r="B13" s="13" t="inlineStr">
+      <c r="B13" s="14" t="inlineStr">
         <is>
           <t>對於工作任務完成度</t>
         </is>
       </c>
-      <c r="C13" s="13" t="inlineStr">
+      <c r="C13" s="14" t="inlineStr">
         <is>
           <t>✓準時上下班工作均能完成 (14-15)
 ✓偶爾加班也能完成工作 (11-13)
@@ -1272,23 +1353,26 @@
 ✓雖經常加班但工作還是延遲完成 (0-1)</t>
         </is>
       </c>
-      <c r="D13" s="6" t="n"/>
+      <c r="D13" s="17" t="n"/>
+      <c r="E13" s="11" t="n"/>
     </row>
     <row r="14" ht="38.5" customHeight="1">
-      <c r="B14" s="21" t="inlineStr">
+      <c r="B14" s="23" t="inlineStr">
         <is>
           <t>*低於等於1或高於等於14分，請說明原因：___________________________</t>
         </is>
       </c>
+      <c r="D14" s="11" t="n"/>
+      <c r="E14" s="11" t="n"/>
     </row>
     <row r="15" ht="38.5" customHeight="1">
       <c r="A15" s="8" t="n"/>
-      <c r="B15" s="14" t="inlineStr">
+      <c r="B15" s="15" t="inlineStr">
         <is>
           <t>※印象中你對受評者在指導與覆核部屬方面，願意給幾分</t>
         </is>
       </c>
-      <c r="C15" s="15" t="inlineStr">
+      <c r="C15" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">✓經常主動指導(領導)部屬 (16-20)
 ✓需經部屬提出並樂意指導(領導) (11-15)
@@ -1297,28 +1381,31 @@
 </t>
         </is>
       </c>
-      <c r="D15" s="6" t="n"/>
+      <c r="D15" s="17" t="n"/>
+      <c r="E15" s="11" t="n"/>
     </row>
     <row r="16" ht="53.5" customHeight="1">
-      <c r="A16" s="18" t="inlineStr">
+      <c r="A16" s="20" t="inlineStr">
         <is>
           <t>領導統御
 30%</t>
         </is>
       </c>
-      <c r="B16" s="19" t="inlineStr">
+      <c r="B16" s="21" t="inlineStr">
         <is>
           <t>*低於等於6分或高於等於16分，請說明原因：________________</t>
         </is>
       </c>
+      <c r="D16" s="11" t="n"/>
+      <c r="E16" s="11" t="n"/>
     </row>
     <row r="17" ht="53.5" customHeight="1">
-      <c r="B17" s="13" t="inlineStr">
+      <c r="B17" s="14" t="inlineStr">
         <is>
           <t>是否願意和受評者一起工作?</t>
         </is>
       </c>
-      <c r="C17" s="13" t="inlineStr">
+      <c r="C17" s="14" t="inlineStr">
         <is>
           <t>✓我很願意跟受評者一起工作(8~10)
 ✓我還算願意跟受評者一起工作(5~7)
@@ -1326,24 +1413,31 @@
 ✓我不願意跟受評者一起工作(0-1)</t>
         </is>
       </c>
-      <c r="D17" s="6" t="n"/>
+      <c r="D17" s="17" t="n"/>
+      <c r="E17" s="11" t="n"/>
     </row>
     <row r="18">
-      <c r="B18" s="21" t="inlineStr">
+      <c r="B18" s="23" t="inlineStr">
         <is>
           <t>*低於等於3分或最高分，請敘述狀況：_________________________</t>
         </is>
       </c>
+      <c r="D18" s="11" t="n"/>
+      <c r="E18" s="11" t="n"/>
     </row>
     <row r="19" ht="50.5" customHeight="1">
-      <c r="B19" s="25" t="n"/>
-      <c r="C19" s="26" t="inlineStr">
+      <c r="B19" s="27" t="n"/>
+      <c r="C19" s="28" t="inlineStr">
         <is>
           <t>總分</t>
         </is>
       </c>
-      <c r="D19" s="27">
+      <c r="D19" s="29">
         <f>SUM(D8:D18)</f>
+        <v/>
+      </c>
+      <c r="E19" s="29">
+        <f>SUM(E8:E18)</f>
         <v/>
       </c>
     </row>
@@ -1358,8 +1452,19 @@
 ), "⚠ 超標！", "")</f>
         <v/>
       </c>
+      <c r="E20" s="6">
+        <f>IF(OR(
+  AND(E19&gt;=90, COUNTIF($D$19:$Z$19, "&gt;=90")/COUNTA($D$19:$Z$19)&gt;0.05),
+  AND(E19&gt;=80,E19&lt;=89, (COUNTIF($D$19:$Z$19, "&gt;=80")-COUNTIF($D$19:$Z$19, "&gt;=90"))/COUNTA($D$19:$Z$19)&gt;0.2),
+  AND(E19&gt;=70,E19&lt;=79, (COUNTIF($D$19:$Z$19, "&gt;=70")-COUNTIF($D$19:$Z$19, "&gt;=80"))/COUNTA($D$19:$Z$19)&gt;0.4),
+  AND(E19&gt;=60,E19&lt;=69, (COUNTIF($D$19:$Z$19, "&gt;=60")-COUNTIF($D$19:$Z$19, "&gt;=70"))/COUNTA($D$19:$Z$19)&gt;0.3),
+  AND(E19&lt;=59, COUNTIF($D$19:$Z$19, "&lt;=59")/COUNTA($D$19:$Z$19)&gt;0.05)
+), "⚠ 超標！", "")</f>
+        <v/>
+      </c>
     </row>
   </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1"/>
   <mergeCells count="14">
     <mergeCell ref="D15:D16"/>
     <mergeCell ref="A12:A14"/>
@@ -1397,14 +1502,14 @@
   </cols>
   <sheetData>
     <row r="1" ht="16" customHeight="1">
-      <c r="A1" s="28" t="inlineStr">
+      <c r="A1" s="30" t="inlineStr">
         <is>
           <t>樂聯工業股份有限公司</t>
         </is>
       </c>
     </row>
     <row r="2" ht="16" customHeight="1">
-      <c r="A2" s="29" t="inlineStr">
+      <c r="A2" s="31" t="inlineStr">
         <is>
           <t>2025年度 年終 績效考核主管複評分表(非主管職)</t>
         </is>
@@ -1440,7 +1545,7 @@
         </is>
       </c>
       <c r="C5" s="3">
-        <f>COUNTIF(D6:P6,"&lt;&gt;")</f>
+        <f>COUNTIF(D6:K6,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -1494,51 +1599,59 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="30" t="inlineStr">
+      <c r="A7" s="32" t="inlineStr">
         <is>
           <t>占比</t>
         </is>
       </c>
-      <c r="B7" s="30" t="inlineStr">
+      <c r="B7" s="32" t="inlineStr">
         <is>
           <t>題目</t>
         </is>
       </c>
-      <c r="C7" s="30" t="inlineStr">
+      <c r="C7" s="32" t="inlineStr">
         <is>
           <t>評分方式</t>
         </is>
       </c>
     </row>
     <row r="8" ht="40" customHeight="1">
-      <c r="A8" s="31" t="inlineStr">
+      <c r="A8" s="33" t="inlineStr">
         <is>
           <t>工作知識20%</t>
         </is>
       </c>
-      <c r="B8" s="11" t="inlineStr">
+      <c r="B8" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">對受評者在該單位的專業知識給分 </t>
         </is>
       </c>
-      <c r="C8" s="11" t="inlineStr">
+      <c r="C8" s="12" t="inlineStr">
         <is>
           <t>0-20</t>
         </is>
       </c>
+      <c r="D8" s="11" t="n"/>
+      <c r="E8" s="11" t="n"/>
+      <c r="F8" s="11" t="n"/>
+      <c r="G8" s="11" t="n"/>
+      <c r="H8" s="11" t="n"/>
+      <c r="I8" s="11" t="n"/>
+      <c r="J8" s="11" t="n"/>
+      <c r="K8" s="11" t="n"/>
     </row>
     <row r="9" ht="74" customHeight="1">
-      <c r="A9" s="31" t="inlineStr">
+      <c r="A9" s="33" t="inlineStr">
         <is>
           <t>團隊溝通協調能力20%</t>
         </is>
       </c>
-      <c r="B9" s="32" t="inlineStr">
+      <c r="B9" s="34" t="inlineStr">
         <is>
           <t>受評者的溝通協調與配合度</t>
         </is>
       </c>
-      <c r="C9" s="33" t="inlineStr">
+      <c r="C9" s="35" t="inlineStr">
         <is>
           <t>✓非常願意溝通協調且配合度極高 (16-20)
 ✓願意溝通協調且配合度高 (12-15)
@@ -1547,16 +1660,24 @@
 ✓非常不願意溝通協調且配合度極低 (0-3)</t>
         </is>
       </c>
+      <c r="D9" s="11" t="n"/>
+      <c r="E9" s="11" t="n"/>
+      <c r="F9" s="11" t="n"/>
+      <c r="G9" s="11" t="n"/>
+      <c r="H9" s="11" t="n"/>
+      <c r="I9" s="11" t="n"/>
+      <c r="J9" s="11" t="n"/>
+      <c r="K9" s="11" t="n"/>
     </row>
     <row r="10" ht="74" customHeight="1">
-      <c r="A10" s="31" t="n"/>
+      <c r="A10" s="33" t="n"/>
       <c r="B10" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">你對於受評者在會議追蹤事項之執行、回覆與結案管理上，是否能依規定期限完成並有效追蹤事項進度之表現評價為何？
 </t>
         </is>
       </c>
-      <c r="C10" s="34" t="inlineStr">
+      <c r="C10" s="36" t="inlineStr">
         <is>
           <t>10分：會議追蹤事項皆能準時完成並主動追蹤，結案完整無需提醒
 7~9分：大多能準時完成，偶有延遲但能主動回覆並完成結案
@@ -1564,35 +1685,43 @@
 4分以下：經常延遲、未追蹤或未完成結案，影響會議執行成效或跨部門作業效率</t>
         </is>
       </c>
-      <c r="D10" s="35" t="n"/>
-      <c r="E10" s="6" t="n"/>
-      <c r="F10" s="6" t="n"/>
-      <c r="G10" s="6" t="n"/>
+      <c r="D10" s="37" t="n"/>
+      <c r="E10" s="17" t="n"/>
+      <c r="F10" s="17" t="n"/>
+      <c r="G10" s="17" t="n"/>
+      <c r="H10" s="11" t="n"/>
+      <c r="I10" s="11" t="n"/>
+      <c r="J10" s="11" t="n"/>
+      <c r="K10" s="11" t="n"/>
     </row>
     <row r="11" ht="50" customHeight="1">
-      <c r="A11" s="31" t="inlineStr">
+      <c r="A11" s="33" t="inlineStr">
         <is>
           <t>工作表現30%</t>
         </is>
       </c>
-      <c r="B11" s="36" t="inlineStr">
+      <c r="B11" s="38" t="inlineStr">
         <is>
           <t>*低於等於4分或高於等於9分，請說明原因：____________________</t>
         </is>
       </c>
-      <c r="C11" s="37" t="n"/>
-      <c r="D11" s="35" t="n"/>
-      <c r="E11" s="6" t="n"/>
-      <c r="F11" s="6" t="n"/>
-      <c r="G11" s="6" t="n"/>
+      <c r="C11" s="39" t="n"/>
+      <c r="D11" s="37" t="n"/>
+      <c r="E11" s="17" t="n"/>
+      <c r="F11" s="17" t="n"/>
+      <c r="G11" s="17" t="n"/>
+      <c r="H11" s="11" t="n"/>
+      <c r="I11" s="11" t="n"/>
+      <c r="J11" s="11" t="n"/>
+      <c r="K11" s="11" t="n"/>
     </row>
     <row r="12" ht="50" customHeight="1">
-      <c r="B12" s="33" t="inlineStr">
+      <c r="B12" s="35" t="inlineStr">
         <is>
           <t>你對於受評者完成工作之品質與完整性評價為何？</t>
         </is>
       </c>
-      <c r="C12" s="33" t="inlineStr">
+      <c r="C12" s="35" t="inlineStr">
         <is>
           <t>10分：工作完整且品質穩定，可直接使用
 7~9分：大致完整，少量修正即可
@@ -1600,15 +1729,29 @@
 4分以下：經常缺漏或品質不佳</t>
         </is>
       </c>
-      <c r="D12" s="6" t="n"/>
+      <c r="D12" s="17" t="n"/>
+      <c r="E12" s="11" t="n"/>
+      <c r="F12" s="11" t="n"/>
+      <c r="G12" s="11" t="n"/>
+      <c r="H12" s="11" t="n"/>
+      <c r="I12" s="11" t="n"/>
+      <c r="J12" s="11" t="n"/>
+      <c r="K12" s="11" t="n"/>
     </row>
     <row r="13" ht="67.5" customHeight="1">
-      <c r="B13" s="38" t="inlineStr">
+      <c r="B13" s="40" t="inlineStr">
         <is>
           <t>*低於等於4分或高於等於9分，請說明原因：____________________</t>
         </is>
       </c>
-      <c r="D13" s="6" t="n"/>
+      <c r="D13" s="17" t="n"/>
+      <c r="E13" s="11" t="n"/>
+      <c r="F13" s="11" t="n"/>
+      <c r="G13" s="11" t="n"/>
+      <c r="H13" s="11" t="n"/>
+      <c r="I13" s="11" t="n"/>
+      <c r="J13" s="11" t="n"/>
+      <c r="K13" s="11" t="n"/>
     </row>
     <row r="14" ht="67.5" customHeight="1">
       <c r="B14" s="9" t="inlineStr">
@@ -1624,24 +1767,38 @@
 4分以下：經常未完成或需他人協助追蹤</t>
         </is>
       </c>
-      <c r="D14" s="6" t="n"/>
+      <c r="D14" s="17" t="n"/>
+      <c r="E14" s="11" t="n"/>
+      <c r="F14" s="11" t="n"/>
+      <c r="G14" s="11" t="n"/>
+      <c r="H14" s="11" t="n"/>
+      <c r="I14" s="11" t="n"/>
+      <c r="J14" s="11" t="n"/>
+      <c r="K14" s="11" t="n"/>
     </row>
     <row r="15" ht="44.5" customHeight="1">
-      <c r="B15" s="36" t="inlineStr">
+      <c r="B15" s="38" t="inlineStr">
         <is>
           <t>*低於等於4分或高於等於9分，請說明原因：____________________</t>
         </is>
       </c>
-      <c r="D15" s="6" t="n"/>
+      <c r="D15" s="17" t="n"/>
+      <c r="E15" s="11" t="n"/>
+      <c r="F15" s="11" t="n"/>
+      <c r="G15" s="11" t="n"/>
+      <c r="H15" s="11" t="n"/>
+      <c r="I15" s="11" t="n"/>
+      <c r="J15" s="11" t="n"/>
+      <c r="K15" s="11" t="n"/>
     </row>
     <row r="16" ht="44.5" customHeight="1">
-      <c r="A16" s="31" t="n"/>
-      <c r="B16" s="33" t="inlineStr">
+      <c r="A16" s="33" t="n"/>
+      <c r="B16" s="35" t="inlineStr">
         <is>
           <t>【行政】工作項目是否能在工時內完成?</t>
         </is>
       </c>
-      <c r="C16" s="33" t="inlineStr">
+      <c r="C16" s="35" t="inlineStr">
         <is>
           <t xml:space="preserve">✓準時上下班工作均能完成 (17-20)
 ✓偶爾加班也能完成工作 (13-16)
@@ -1652,21 +1809,35 @@
 </t>
         </is>
       </c>
-      <c r="D16" s="6" t="n"/>
+      <c r="D16" s="17" t="n"/>
+      <c r="E16" s="11" t="n"/>
+      <c r="F16" s="11" t="n"/>
+      <c r="G16" s="11" t="n"/>
+      <c r="H16" s="11" t="n"/>
+      <c r="I16" s="11" t="n"/>
+      <c r="J16" s="11" t="n"/>
+      <c r="K16" s="11" t="n"/>
     </row>
     <row r="17" ht="47.5" customHeight="1">
-      <c r="A17" s="39" t="inlineStr">
+      <c r="A17" s="41" t="inlineStr">
         <is>
           <t>工作態度
 30%</t>
         </is>
       </c>
-      <c r="B17" s="38" t="inlineStr">
+      <c r="B17" s="40" t="inlineStr">
         <is>
           <t>*低於等於2分或高於等於16分，請說明原因：_________________________</t>
         </is>
       </c>
-      <c r="D17" s="6" t="n"/>
+      <c r="D17" s="17" t="n"/>
+      <c r="E17" s="11" t="n"/>
+      <c r="F17" s="11" t="n"/>
+      <c r="G17" s="11" t="n"/>
+      <c r="H17" s="11" t="n"/>
+      <c r="I17" s="11" t="n"/>
+      <c r="J17" s="11" t="n"/>
+      <c r="K17" s="11" t="n"/>
     </row>
     <row r="18" ht="47.5" customHeight="1">
       <c r="B18" s="9" t="inlineStr">
@@ -1682,27 +1853,69 @@
 4分以下：執行品質不穩定或常需重工</t>
         </is>
       </c>
-      <c r="D18" s="6" t="n"/>
+      <c r="D18" s="17" t="n"/>
+      <c r="E18" s="11" t="n"/>
+      <c r="F18" s="11" t="n"/>
+      <c r="G18" s="11" t="n"/>
+      <c r="H18" s="11" t="n"/>
+      <c r="I18" s="11" t="n"/>
+      <c r="J18" s="11" t="n"/>
+      <c r="K18" s="11" t="n"/>
     </row>
     <row r="19" ht="71.5" customHeight="1">
-      <c r="B19" s="36" t="inlineStr">
+      <c r="B19" s="38" t="inlineStr">
         <is>
           <t>*低於等於2分或高於等於9分，請說明原因： _________________________</t>
         </is>
       </c>
-      <c r="D19" s="6" t="n"/>
+      <c r="D19" s="17" t="n"/>
+      <c r="E19" s="11" t="n"/>
+      <c r="F19" s="11" t="n"/>
+      <c r="G19" s="11" t="n"/>
+      <c r="H19" s="11" t="n"/>
+      <c r="I19" s="11" t="n"/>
+      <c r="J19" s="11" t="n"/>
+      <c r="K19" s="11" t="n"/>
     </row>
     <row r="20" ht="23.5" customHeight="1">
-      <c r="C20" s="26" t="inlineStr">
+      <c r="C20" s="28" t="inlineStr">
         <is>
           <t>總分</t>
         </is>
       </c>
-      <c r="D20" s="27">
+      <c r="D20" s="29">
         <f>SUM(D8:D19)</f>
         <v/>
       </c>
-      <c r="BK20" s="40" t="n"/>
+      <c r="E20" s="29">
+        <f>SUM(E8:E19)</f>
+        <v/>
+      </c>
+      <c r="F20" s="29">
+        <f>SUM(F8:F19)</f>
+        <v/>
+      </c>
+      <c r="G20" s="29">
+        <f>SUM(G8:G19)</f>
+        <v/>
+      </c>
+      <c r="H20" s="29">
+        <f>SUM(H8:H19)</f>
+        <v/>
+      </c>
+      <c r="I20" s="29">
+        <f>SUM(I8:I19)</f>
+        <v/>
+      </c>
+      <c r="J20" s="29">
+        <f>SUM(J8:J19)</f>
+        <v/>
+      </c>
+      <c r="K20" s="29">
+        <f>SUM(K8:K19)</f>
+        <v/>
+      </c>
+      <c r="BK20" s="42" t="n"/>
     </row>
     <row r="21">
       <c r="D21" s="6">
@@ -1715,8 +1928,79 @@
 ), "⚠ 超標！", "")</f>
         <v/>
       </c>
+      <c r="E21" s="6">
+        <f>IF(OR(
+  AND(E20&gt;=90, COUNTIF($D$20:$Z$20, "&gt;=90")/COUNTA($D$20:$Z$20)&gt;0.05),
+  AND(E20&gt;=80,E20&lt;=89, (COUNTIF($D$20:$Z$20, "&gt;=80")-COUNTIF($D$20:$Z$20, "&gt;=90"))/COUNTA($D$20:$Z$20)&gt;0.2),
+  AND(E20&gt;=70,E20&lt;=79, (COUNTIF($D$20:$Z$20, "&gt;=70")-COUNTIF($D$20:$Z$20, "&gt;=80"))/COUNTA($D$20:$Z$20)&gt;0.4),
+  AND(E20&gt;=60,E20&lt;=69, (COUNTIF($D$20:$Z$20, "&gt;=60")-COUNTIF($D$20:$Z$20, "&gt;=70"))/COUNTA($D$20:$Z$20)&gt;0.3),
+  AND(E20&lt;=59, COUNTIF($D$20:$Z$20, "&lt;=59")/COUNTA($D$20:$Z$20)&gt;0.05)
+), "⚠ 超標！", "")</f>
+        <v/>
+      </c>
+      <c r="F21" s="6">
+        <f>IF(OR(
+  AND(F20&gt;=90, COUNTIF($D$20:$Z$20, "&gt;=90")/COUNTA($D$20:$Z$20)&gt;0.05),
+  AND(F20&gt;=80,F20&lt;=89, (COUNTIF($D$20:$Z$20, "&gt;=80")-COUNTIF($D$20:$Z$20, "&gt;=90"))/COUNTA($D$20:$Z$20)&gt;0.2),
+  AND(F20&gt;=70,F20&lt;=79, (COUNTIF($D$20:$Z$20, "&gt;=70")-COUNTIF($D$20:$Z$20, "&gt;=80"))/COUNTA($D$20:$Z$20)&gt;0.4),
+  AND(F20&gt;=60,F20&lt;=69, (COUNTIF($D$20:$Z$20, "&gt;=60")-COUNTIF($D$20:$Z$20, "&gt;=70"))/COUNTA($D$20:$Z$20)&gt;0.3),
+  AND(F20&lt;=59, COUNTIF($D$20:$Z$20, "&lt;=59")/COUNTA($D$20:$Z$20)&gt;0.05)
+), "⚠ 超標！", "")</f>
+        <v/>
+      </c>
+      <c r="G21" s="6">
+        <f>IF(OR(
+  AND(G20&gt;=90, COUNTIF($D$20:$Z$20, "&gt;=90")/COUNTA($D$20:$Z$20)&gt;0.05),
+  AND(G20&gt;=80,G20&lt;=89, (COUNTIF($D$20:$Z$20, "&gt;=80")-COUNTIF($D$20:$Z$20, "&gt;=90"))/COUNTA($D$20:$Z$20)&gt;0.2),
+  AND(G20&gt;=70,G20&lt;=79, (COUNTIF($D$20:$Z$20, "&gt;=70")-COUNTIF($D$20:$Z$20, "&gt;=80"))/COUNTA($D$20:$Z$20)&gt;0.4),
+  AND(G20&gt;=60,G20&lt;=69, (COUNTIF($D$20:$Z$20, "&gt;=60")-COUNTIF($D$20:$Z$20, "&gt;=70"))/COUNTA($D$20:$Z$20)&gt;0.3),
+  AND(G20&lt;=59, COUNTIF($D$20:$Z$20, "&lt;=59")/COUNTA($D$20:$Z$20)&gt;0.05)
+), "⚠ 超標！", "")</f>
+        <v/>
+      </c>
+      <c r="H21" s="6">
+        <f>IF(OR(
+  AND(H20&gt;=90, COUNTIF($D$20:$Z$20, "&gt;=90")/COUNTA($D$20:$Z$20)&gt;0.05),
+  AND(H20&gt;=80,H20&lt;=89, (COUNTIF($D$20:$Z$20, "&gt;=80")-COUNTIF($D$20:$Z$20, "&gt;=90"))/COUNTA($D$20:$Z$20)&gt;0.2),
+  AND(H20&gt;=70,H20&lt;=79, (COUNTIF($D$20:$Z$20, "&gt;=70")-COUNTIF($D$20:$Z$20, "&gt;=80"))/COUNTA($D$20:$Z$20)&gt;0.4),
+  AND(H20&gt;=60,H20&lt;=69, (COUNTIF($D$20:$Z$20, "&gt;=60")-COUNTIF($D$20:$Z$20, "&gt;=70"))/COUNTA($D$20:$Z$20)&gt;0.3),
+  AND(H20&lt;=59, COUNTIF($D$20:$Z$20, "&lt;=59")/COUNTA($D$20:$Z$20)&gt;0.05)
+), "⚠ 超標！", "")</f>
+        <v/>
+      </c>
+      <c r="I21" s="6">
+        <f>IF(OR(
+  AND(I20&gt;=90, COUNTIF($D$20:$Z$20, "&gt;=90")/COUNTA($D$20:$Z$20)&gt;0.05),
+  AND(I20&gt;=80,I20&lt;=89, (COUNTIF($D$20:$Z$20, "&gt;=80")-COUNTIF($D$20:$Z$20, "&gt;=90"))/COUNTA($D$20:$Z$20)&gt;0.2),
+  AND(I20&gt;=70,I20&lt;=79, (COUNTIF($D$20:$Z$20, "&gt;=70")-COUNTIF($D$20:$Z$20, "&gt;=80"))/COUNTA($D$20:$Z$20)&gt;0.4),
+  AND(I20&gt;=60,I20&lt;=69, (COUNTIF($D$20:$Z$20, "&gt;=60")-COUNTIF($D$20:$Z$20, "&gt;=70"))/COUNTA($D$20:$Z$20)&gt;0.3),
+  AND(I20&lt;=59, COUNTIF($D$20:$Z$20, "&lt;=59")/COUNTA($D$20:$Z$20)&gt;0.05)
+), "⚠ 超標！", "")</f>
+        <v/>
+      </c>
+      <c r="J21" s="6">
+        <f>IF(OR(
+  AND(J20&gt;=90, COUNTIF($D$20:$Z$20, "&gt;=90")/COUNTA($D$20:$Z$20)&gt;0.05),
+  AND(J20&gt;=80,J20&lt;=89, (COUNTIF($D$20:$Z$20, "&gt;=80")-COUNTIF($D$20:$Z$20, "&gt;=90"))/COUNTA($D$20:$Z$20)&gt;0.2),
+  AND(J20&gt;=70,J20&lt;=79, (COUNTIF($D$20:$Z$20, "&gt;=70")-COUNTIF($D$20:$Z$20, "&gt;=80"))/COUNTA($D$20:$Z$20)&gt;0.4),
+  AND(J20&gt;=60,J20&lt;=69, (COUNTIF($D$20:$Z$20, "&gt;=60")-COUNTIF($D$20:$Z$20, "&gt;=70"))/COUNTA($D$20:$Z$20)&gt;0.3),
+  AND(J20&lt;=59, COUNTIF($D$20:$Z$20, "&lt;=59")/COUNTA($D$20:$Z$20)&gt;0.05)
+), "⚠ 超標！", "")</f>
+        <v/>
+      </c>
+      <c r="K21" s="6">
+        <f>IF(OR(
+  AND(K20&gt;=90, COUNTIF($D$20:$Z$20, "&gt;=90")/COUNTA($D$20:$Z$20)&gt;0.05),
+  AND(K20&gt;=80,K20&lt;=89, (COUNTIF($D$20:$Z$20, "&gt;=80")-COUNTIF($D$20:$Z$20, "&gt;=90"))/COUNTA($D$20:$Z$20)&gt;0.2),
+  AND(K20&gt;=70,K20&lt;=79, (COUNTIF($D$20:$Z$20, "&gt;=70")-COUNTIF($D$20:$Z$20, "&gt;=80"))/COUNTA($D$20:$Z$20)&gt;0.4),
+  AND(K20&gt;=60,K20&lt;=69, (COUNTIF($D$20:$Z$20, "&gt;=60")-COUNTIF($D$20:$Z$20, "&gt;=70"))/COUNTA($D$20:$Z$20)&gt;0.3),
+  AND(K20&lt;=59, COUNTIF($D$20:$Z$20, "&lt;=59")/COUNTA($D$20:$Z$20)&gt;0.05)
+), "⚠ 超標！", "")</f>
+        <v/>
+      </c>
     </row>
   </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1"/>
   <mergeCells count="10">
     <mergeCell ref="A2:I2"/>
     <mergeCell ref="A17:A19"/>
